--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDBF688-E602-4F06-99C9-CD98AA7C6D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F86E6B7BF5071D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDFED12F-793B-42E3-A4EC-444A814CB9EB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 09-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 14-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F86E6B7BF5071D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDFED12F-793B-42E3-A4EC-444A814CB9EB}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F396E75AE3C70D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB6413B4-EA29-4E90-9ACC-3C84CC1E12B8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F396E75AE3C70D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB6413B4-EA29-4E90-9ACC-3C84CC1E12B8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABAA9D3-8C9C-4B70-9866-EFA36058E7DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABAA9D3-8C9C-4B70-9866-EFA36058E7DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38031835-DA09-4B86-9E78-8C2AE2CFC41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 14-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 17-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38031835-DA09-4B86-9E78-8C2AE2CFC41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B3F3A9-460F-4C8E-897A-DD4DD830B541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B3F3A9-460F-4C8E-897A-DD4DD830B541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3FFBFEB7BE5470D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0207D3F-40A9-45EF-BEEC-7473CD807F24}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 17-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 18-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3FFBFEB7BE5470D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0207D3F-40A9-45EF-BEEC-7473CD807F24}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3FA7DEF4A75470D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9C497BD-7805-4D48-9BBF-885604EF52A4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 18-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 21-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3FA7DEF4A75470D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9C497BD-7805-4D48-9BBF-885604EF52A4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833B29F5-575B-4F30-8C36-37A9A1C2A3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833B29F5-575B-4F30-8C36-37A9A1C2A3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C43AEF-8C3F-4CE4-B028-71F87464431E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 21-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 22-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C43AEF-8C3F-4CE4-B028-71F87464431E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD16B40-B3EB-4483-B869-7D3CC9F4948C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD16B40-B3EB-4483-B869-7D3CC9F4948C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAB628A-439F-4113-9FA9-E03A3BD99D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 22-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 23-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAB628A-439F-4113-9FA9-E03A3BD99D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F209EB59D6A71D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05962942-3C95-4878-B5A7-CC682F1F4A47}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F209EB59D6A71D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05962942-3C95-4878-B5A7-CC682F1F4A47}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F643EF39A5A70D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AA14E31-AAFE-49EB-8C26-8A6860E6EC7A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 23-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 24-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F643EF39A5A70D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AA14E31-AAFE-49EB-8C26-8A6860E6EC7A}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F541EF3A93070D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E488FD09-F388-4226-B698-AAB2B844C413}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F541EF3A93070D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E488FD09-F388-4226-B698-AAB2B844C413}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6488B48-9035-40CD-BFED-6C93565D8226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 24-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 28-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6488B48-9035-40CD-BFED-6C93565D8226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F966EF6AED271D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA793AF-059D-4C09-A0B3-C6F018A2713D}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 28-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 02-10-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD16B40-B3EB-4483-B869-7D3CC9F4948C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC64EC2D-BDDF-4264-A920-695AAEE084FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 22-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 07-10-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F966EF6AED271D8F5B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA793AF-059D-4C09-A0B3-C6F018A2713D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3225FD-CA49-4B30-9335-BA9D365A61A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 02-10-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 07-10-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3225FD-CA49-4B30-9335-BA9D365A61A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F94667498C671D8F5BD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F4BCA8-93D5-4AD8-8712-3D1BF2D33197}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 07-10-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 08-10-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3F94667498C671D8F5BD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F4BCA8-93D5-4AD8-8712-3D1BF2D33197}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B88C159-BF21-4693-B7CE-D1E76327CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 08-10-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 09-10-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B88C159-BF21-4693-B7CE-D1E76327CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2624C1-A68D-47AB-B619-109CAAB41BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2624C1-A68D-47AB-B619-109CAAB41BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AD7ABBB0486536F1AD8A3FDA7E778C9671D8F5BD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78217B27-1AE7-4232-8FCA-29FAEBAFE6AF}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 09-10-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 23-10-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
